--- a/Mentorias/2026-10-12_Julio/01_Valor_Medio_Investido.xlsx
+++ b/Mentorias/2026-10-12_Julio/01_Valor_Medio_Investido.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\mestrado\coleta_dados_petr4\Mentorias\2026-10-12_Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C70B149E-E832-4934-8973-E11134FBB059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FA79342-E15C-439F-9496-E3B6240271C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="168">
   <si>
     <t>Ticker</t>
   </si>
@@ -46,8 +46,8 @@
     <t>Empresa</t>
   </si>
   <si>
-    <t>Data-base
-(acionistas)</t>
+    <t>Data da
+assembleia</t>
   </si>
   <si>
     <t>Acionistas
@@ -78,7 +78,7 @@
     <t>VALE S.A.</t>
   </si>
   <si>
-    <t>2026-12-31</t>
+    <t>2026-04-30</t>
   </si>
   <si>
     <t>ITUB4</t>
@@ -87,24 +87,36 @@
     <t>ITAU UNIBANCO HOLDING S.A.</t>
   </si>
   <si>
+    <t>2026-05-19</t>
+  </si>
+  <si>
     <t>PETR4</t>
   </si>
   <si>
     <t>PETROLEO BRASILEIRO S.A. PETROBRAS</t>
   </si>
   <si>
+    <t>2026-04-16</t>
+  </si>
+  <si>
     <t>SBSP3</t>
   </si>
   <si>
     <t>CIA SANEAMENTO BASICO EST SAO PAULO</t>
   </si>
   <si>
+    <t>2026-04-28</t>
+  </si>
+  <si>
     <t>BBDC4</t>
   </si>
   <si>
     <t>BCO BRADESCO S.A.</t>
   </si>
   <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
     <t>B3SA3</t>
   </si>
   <si>
@@ -129,12 +141,18 @@
     <t>BCO BRASIL S.A.</t>
   </si>
   <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
     <t>ABEV3</t>
   </si>
   <si>
     <t>AMBEV S.A.</t>
   </si>
   <si>
+    <t>2026-08-13</t>
+  </si>
+  <si>
     <t>Fontes: CVM/dados/distribuicao_capital_papeis.csv (Formulário de Referência da CVM — acionistas e ações em circulação, por assembleia) + CVM/dados/ohlcv_b3.csv (preço de fechamento em 2026-09-15). Datas-base diferentes entre as duas fontes — é a mesma limitação já registrada na planilha 16 da pasta de 16/09.</t>
   </si>
   <si>
@@ -153,6 +171,9 @@
     <t>KLABIN S.A.</t>
   </si>
   <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
     <t>BBSE3</t>
   </si>
   <si>
@@ -165,6 +186,9 @@
     <t>BCO SANTANDER (BRASIL) S.A.</t>
   </si>
   <si>
+    <t>2026-01-15</t>
+  </si>
+  <si>
     <t>MGLU3</t>
   </si>
   <si>
@@ -183,18 +207,27 @@
     <t>ENGIE BRASIL ENERGIA S.A.</t>
   </si>
   <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
     <t>GGBR4</t>
   </si>
   <si>
     <t>GERDAU S.A.</t>
   </si>
   <si>
+    <t>2026-04-15</t>
+  </si>
+  <si>
     <t>GOAU4</t>
   </si>
   <si>
     <t>METALURGICA GERDAU S.A.</t>
   </si>
   <si>
+    <t>2026-04-17</t>
+  </si>
+  <si>
     <t>PRIO3</t>
   </si>
   <si>
@@ -213,6 +246,9 @@
     <t>PORTO SEGURO S.A.</t>
   </si>
   <si>
+    <t>2026-03-31</t>
+  </si>
+  <si>
     <t>COGN3</t>
   </si>
   <si>
@@ -225,12 +261,18 @@
     <t>ALLOS S.A.</t>
   </si>
   <si>
+    <t>2026-05-14</t>
+  </si>
+  <si>
     <t>USIM5</t>
   </si>
   <si>
     <t>USINAS SID DE MINAS GERAIS S.A.-USIMINAS</t>
   </si>
   <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
     <t>CPFE3</t>
   </si>
   <si>
@@ -243,6 +285,9 @@
     <t>CVC BRASIL OPERADORA E AGÊNCIA DE VIAGENS S.A.</t>
   </si>
   <si>
+    <t>2026-05-05</t>
+  </si>
+  <si>
     <t>LREN3</t>
   </si>
   <si>
@@ -255,18 +300,21 @@
     <t>TIM S.A.</t>
   </si>
   <si>
+    <t>SUZB3</t>
+  </si>
+  <si>
+    <t>SUZANO S.A.</t>
+  </si>
+  <si>
+    <t>2026-08-19</t>
+  </si>
+  <si>
     <t>CSNA3</t>
   </si>
   <si>
     <t>CIA SIDERURGICA NACIONAL</t>
   </si>
   <si>
-    <t>SUZB3</t>
-  </si>
-  <si>
-    <t>SUZANO S.A.</t>
-  </si>
-  <si>
     <t>EQTL3</t>
   </si>
   <si>
@@ -291,6 +339,9 @@
     <t>BRAVA ENERGIA S.A.</t>
   </si>
   <si>
+    <t>2026-04-20</t>
+  </si>
+  <si>
     <t>BEEF3</t>
   </si>
   <si>
@@ -309,6 +360,9 @@
     <t>REDE D'OR SÃO LUIZ S.A.</t>
   </si>
   <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
     <t>VBBR3</t>
   </si>
   <si>
@@ -321,91 +375,103 @@
     <t>BRASKEM S.A.</t>
   </si>
   <si>
+    <t>2026-06-08</t>
+  </si>
+  <si>
+    <t>NTCO3</t>
+  </si>
+  <si>
+    <t>NATURA COSMÉTICOS S.A.</t>
+  </si>
+  <si>
+    <t>TOTS3</t>
+  </si>
+  <si>
+    <t>TOTVS S.A.</t>
+  </si>
+  <si>
+    <t>ASAI3</t>
+  </si>
+  <si>
+    <t>SENDAS DISTRIBUIDORA S.A.</t>
+  </si>
+  <si>
+    <t>HYPE3</t>
+  </si>
+  <si>
+    <t>HYPERA S.A.</t>
+  </si>
+  <si>
+    <t>2026-04-27</t>
+  </si>
+  <si>
+    <t>LWSA3</t>
+  </si>
+  <si>
+    <t>LWSA S/A</t>
+  </si>
+  <si>
+    <t>HAPV3</t>
+  </si>
+  <si>
+    <t>HAPVIDA PARTICIPAÇÕES E INVESTIMENTOS S.A.</t>
+  </si>
+  <si>
+    <t>RAIL3</t>
+  </si>
+  <si>
+    <t>RUMO S.A.</t>
+  </si>
+  <si>
+    <t>UGPA3</t>
+  </si>
+  <si>
+    <t>ULTRAPAR PARTICIPACOES S.A.</t>
+  </si>
+  <si>
+    <t>SMTO3</t>
+  </si>
+  <si>
+    <t>SAO MARTINHO S.A.</t>
+  </si>
+  <si>
+    <t>2025-07-25</t>
+  </si>
+  <si>
+    <t>CCRO3</t>
+  </si>
+  <si>
+    <t>MOTIVA INFRAESTRUTURA DE MOBILIDADE S.A.</t>
+  </si>
+  <si>
+    <t>LIGT3</t>
+  </si>
+  <si>
+    <t>LIGHT S.A. - EM RECUPERAÇÃO JUDICIAL</t>
+  </si>
+  <si>
+    <t>2026-08-20</t>
+  </si>
+  <si>
+    <t>MULT3</t>
+  </si>
+  <si>
+    <t>MULTIPLAN - EMPREEND IMOBILIARIOS S.A.</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>YDUQ3</t>
+  </si>
+  <si>
+    <t>YDUQS PARTICIPACOES S.A.</t>
+  </si>
+  <si>
     <t>ENGI11</t>
   </si>
   <si>
-    <t>ENERGISA S.A.</t>
-  </si>
-  <si>
-    <t>NTCO3</t>
-  </si>
-  <si>
-    <t>NATURA COSMÉTICOS S.A.</t>
-  </si>
-  <si>
-    <t>TOTS3</t>
-  </si>
-  <si>
-    <t>TOTVS S.A.</t>
-  </si>
-  <si>
-    <t>ASAI3</t>
-  </si>
-  <si>
-    <t>SENDAS DISTRIBUIDORA S.A.</t>
-  </si>
-  <si>
-    <t>HYPE3</t>
-  </si>
-  <si>
-    <t>HYPERA S.A.</t>
-  </si>
-  <si>
-    <t>LWSA3</t>
-  </si>
-  <si>
-    <t>LWSA S/A</t>
-  </si>
-  <si>
-    <t>HAPV3</t>
-  </si>
-  <si>
-    <t>HAPVIDA PARTICIPAÇÕES E INVESTIMENTOS S.A.</t>
-  </si>
-  <si>
-    <t>RAIL3</t>
-  </si>
-  <si>
-    <t>RUMO S.A.</t>
-  </si>
-  <si>
-    <t>UGPA3</t>
-  </si>
-  <si>
-    <t>ULTRAPAR PARTICIPACOES S.A.</t>
-  </si>
-  <si>
-    <t>SMTO3</t>
-  </si>
-  <si>
-    <t>SAO MARTINHO S.A.</t>
-  </si>
-  <si>
-    <t>2026-03-31</t>
-  </si>
-  <si>
-    <t>CCRO3</t>
-  </si>
-  <si>
-    <t>MOTIVA INFRAESTRUTURA DE MOBILIDADE S.A.</t>
-  </si>
-  <si>
-    <t>LIGT3</t>
-  </si>
-  <si>
-    <t>LIGHT S.A. - EM RECUPERAÇÃO JUDICIAL</t>
-  </si>
-  <si>
-    <t>MULT3</t>
-  </si>
-  <si>
-    <t>MULTIPLAN - EMPREEND IMOBILIARIOS S.A.</t>
-  </si>
-  <si>
-    <t>YDUQ3</t>
-  </si>
-  <si>
-    <t>YDUQS PARTICIPACOES S.A.</t>
+    <t>ENERGISA SUL-SUDESTE - DISTRIBUIDORA DE ENERGIA S/A</t>
   </si>
   <si>
     <t>RENT3</t>
@@ -414,6 +480,9 @@
     <t>LOCALIZA FLEET S.A.</t>
   </si>
   <si>
+    <t>2026-03-17</t>
+  </si>
+  <si>
     <t>OIBR3</t>
   </si>
   <si>
@@ -426,12 +495,18 @@
     <t>IGUATEMI EMPRESA DE SHOPPING CENTERS S.A</t>
   </si>
   <si>
+    <t>2025-04-17</t>
+  </si>
+  <si>
     <t>ELET3</t>
   </si>
   <si>
     <t>AXIA ENERGIA S.A.</t>
   </si>
   <si>
+    <t>2026-08-28</t>
+  </si>
+  <si>
     <t>sem preço coletado</t>
   </si>
   <si>
@@ -450,13 +525,16 @@
     <t>EMBRAER S.A.</t>
   </si>
   <si>
+    <t>2026-05-06</t>
+  </si>
+  <si>
     <t>GOLL4</t>
   </si>
   <si>
     <t>GOL LINHAS AEREAS INTELIGENTES S.A.</t>
   </si>
   <si>
-    <t>2025-12-31</t>
+    <t>2026-02-23</t>
   </si>
   <si>
     <t>AZUL4</t>
@@ -469,6 +547,9 @@
   </si>
   <si>
     <t>BRF S.A.</t>
+  </si>
+  <si>
+    <t>2025-09-26</t>
   </si>
 </sst>
 </file>
@@ -1000,7 +1081,7 @@
         <v>12</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D3" s="10">
         <v>667798</v>
@@ -1022,13 +1103,13 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D4" s="4">
         <v>1183775</v>
@@ -1050,13 +1131,13 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D5" s="10">
         <v>60606</v>
@@ -1078,13 +1159,13 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D6" s="4">
         <v>882476</v>
@@ -1106,10 +1187,10 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>10</v>
@@ -1118,26 +1199,26 @@
         <v>294151</v>
       </c>
       <c r="E7" s="10">
-        <v>4985893391</v>
+        <v>4972065060</v>
       </c>
       <c r="F7" s="11">
         <f t="shared" si="0"/>
-        <v>16950.115386315192</v>
+        <v>16903.104391961951</v>
       </c>
       <c r="G7" s="12">
         <v>17.420000076293949</v>
       </c>
       <c r="H7" s="13">
         <f t="shared" si="1"/>
-        <v>295271.01132280187</v>
+        <v>294452.07979758177</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>10</v>
@@ -1162,10 +1243,10 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>10</v>
@@ -1190,13 +1271,13 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="D10" s="4">
         <v>1551254</v>
@@ -1218,13 +1299,13 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="D11" s="10">
         <v>213087</v>
@@ -1246,7 +1327,7 @@
     </row>
     <row r="13" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="24" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B13" s="25"/>
       <c r="C13" s="25"/>
@@ -1258,7 +1339,7 @@
     </row>
     <row r="14" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="24" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B14" s="25"/>
       <c r="C14" s="25"/>
@@ -1270,7 +1351,7 @@
     </row>
     <row r="15" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="24" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B15" s="25"/>
       <c r="C15" s="25"/>
@@ -1282,7 +1363,7 @@
     </row>
     <row r="16" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="24" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B16" s="25"/>
       <c r="C16" s="25"/>
@@ -1345,13 +1426,13 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="D2" s="16">
         <v>1551254</v>
@@ -1373,13 +1454,13 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D3" s="16">
         <v>1183775</v>
@@ -1401,10 +1482,10 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C4" s="15" t="s">
         <v>10</v>
@@ -1429,13 +1510,13 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D5" s="16">
         <v>882476</v>
@@ -1491,7 +1572,7 @@
         <v>12</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D7" s="16">
         <v>667798</v>
@@ -1513,13 +1594,13 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="D8" s="4">
         <v>663810</v>
@@ -1541,10 +1622,10 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>10</v>
@@ -1569,13 +1650,13 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="D10" s="4">
         <v>337376</v>
@@ -1597,10 +1678,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>10</v>
@@ -1625,10 +1706,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C12" s="15" t="s">
         <v>10</v>
@@ -1637,29 +1718,29 @@
         <v>294151</v>
       </c>
       <c r="E12" s="16">
-        <v>4985893391</v>
+        <v>4972065060</v>
       </c>
       <c r="F12" s="17">
         <f t="shared" si="0"/>
-        <v>16950.115386315192</v>
+        <v>16903.104391961951</v>
       </c>
       <c r="G12" s="18">
         <v>17.420000076293949</v>
       </c>
       <c r="H12" s="19">
         <f t="shared" si="1"/>
-        <v>295271.01132280187</v>
+        <v>294452.07979758177</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D13" s="10">
         <v>273626</v>
@@ -1681,13 +1762,13 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="D14" s="4">
         <v>264564</v>
@@ -1709,13 +1790,13 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="D15" s="10">
         <v>214168</v>
@@ -1737,13 +1818,13 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="D16" s="16">
         <v>213087</v>
@@ -1765,13 +1846,13 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>10</v>
+        <v>59</v>
       </c>
       <c r="D17" s="10">
         <v>168315</v>
@@ -1793,13 +1874,13 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>10</v>
+        <v>59</v>
       </c>
       <c r="D18" s="4">
         <v>161783</v>
@@ -1821,10 +1902,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="C19" s="9" t="s">
         <v>10</v>
@@ -1849,13 +1930,13 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="D20" s="4">
         <v>140419</v>
@@ -1877,13 +1958,13 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D21" s="10">
         <v>138518</v>
@@ -1905,10 +1986,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C22" s="15" t="s">
         <v>10</v>
@@ -1933,13 +2014,13 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>10</v>
+        <v>71</v>
       </c>
       <c r="D23" s="10">
         <v>119890</v>
@@ -1961,13 +2042,13 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>10</v>
+        <v>74</v>
       </c>
       <c r="D24" s="4">
         <v>115411</v>
@@ -1989,13 +2070,13 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="D25" s="10">
         <v>106796</v>
@@ -2017,13 +2098,13 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>10</v>
+        <v>79</v>
       </c>
       <c r="D26" s="4">
         <v>105312</v>
@@ -2045,13 +2126,13 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="D27" s="10">
         <v>104687</v>
@@ -2073,13 +2154,13 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="D28" s="4">
         <v>99143</v>
@@ -2101,66 +2182,66 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="D29" s="10">
-        <v>89261</v>
+        <v>88909</v>
       </c>
       <c r="E29" s="10">
-        <v>727462410</v>
+        <v>608216821</v>
       </c>
       <c r="F29" s="11">
         <f t="shared" si="0"/>
-        <v>8149.8348662909893</v>
+        <v>6840.8914845516201</v>
       </c>
       <c r="G29" s="12">
-        <v>6.2100000381469727</v>
+        <v>47.560001373291023</v>
       </c>
       <c r="H29" s="13">
         <f t="shared" si="1"/>
-        <v>50610.474830558574</v>
+        <v>325352.80839980993</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="D30" s="4">
-        <v>88909</v>
+        <v>84063</v>
       </c>
       <c r="E30" s="4">
-        <v>608216821</v>
+        <v>727421210</v>
       </c>
       <c r="F30" s="5">
         <f t="shared" si="0"/>
-        <v>6840.8914845516201</v>
+        <v>8653.2863447652362</v>
       </c>
       <c r="G30" s="6">
-        <v>47.560001373291023</v>
+        <v>6.2100000381469727</v>
       </c>
       <c r="H30" s="7">
         <f t="shared" si="1"/>
-        <v>325352.80839980993</v>
+        <v>53736.908531088797</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="C31" s="9" t="s">
         <v>10</v>
@@ -2185,10 +2266,10 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>10</v>
@@ -2213,13 +2294,13 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D33" s="10">
         <v>73122</v>
@@ -2241,13 +2322,13 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="D34" s="4">
         <v>71939</v>
@@ -2269,13 +2350,13 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D35" s="10">
         <v>64240</v>
@@ -2297,13 +2378,13 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="D36" s="4">
         <v>61765</v>
@@ -2325,13 +2406,13 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="14" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D37" s="16">
         <v>60606</v>
@@ -2353,13 +2434,13 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="D38" s="4">
         <v>56682</v>
@@ -2381,13 +2462,13 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="D39" s="10">
         <v>54041</v>
@@ -2409,13 +2490,13 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>10</v>
+        <v>109</v>
       </c>
       <c r="D40" s="4">
         <v>52331</v>
@@ -2437,405 +2518,405 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="D41" s="10">
-        <v>51432</v>
+        <v>48012</v>
       </c>
       <c r="E41" s="10">
-        <v>1791454506</v>
+        <v>727229572</v>
       </c>
       <c r="F41" s="11">
         <f t="shared" si="2"/>
-        <v>34831.515515632294</v>
+        <v>15146.829375989337</v>
       </c>
       <c r="G41" s="12">
-        <v>51.529998779296882</v>
+        <v>7.929999828338623</v>
       </c>
       <c r="H41" s="13">
         <f t="shared" si="3"/>
-        <v>1794867.9520015926</v>
+        <v>120114.35435146985</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="D42" s="4">
-        <v>48012</v>
+        <v>46146</v>
       </c>
       <c r="E42" s="4">
-        <v>727229572</v>
+        <v>515889217</v>
       </c>
       <c r="F42" s="5">
         <f t="shared" si="2"/>
-        <v>15146.829375989337</v>
+        <v>11179.500216703505</v>
       </c>
       <c r="G42" s="6">
-        <v>7.929999828338623</v>
+        <v>33.830001831054688</v>
       </c>
       <c r="H42" s="7">
         <f t="shared" si="3"/>
-        <v>120114.35435146985</v>
+        <v>378202.51280135586</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="D43" s="10">
-        <v>46146</v>
+        <v>40026</v>
       </c>
       <c r="E43" s="10">
-        <v>515889217</v>
+        <v>1335651252</v>
       </c>
       <c r="F43" s="11">
         <f t="shared" si="2"/>
-        <v>11179.500216703505</v>
+        <v>33369.591065807224</v>
       </c>
       <c r="G43" s="12">
-        <v>33.830001831054688</v>
+        <v>9.6499996185302717</v>
       </c>
       <c r="H43" s="13">
         <f t="shared" si="3"/>
-        <v>378202.51280135586</v>
+        <v>322016.54105555086</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>10</v>
+        <v>118</v>
       </c>
       <c r="D44" s="4">
-        <v>40026</v>
+        <v>37858</v>
       </c>
       <c r="E44" s="4">
-        <v>1335651252</v>
+        <v>296007718</v>
       </c>
       <c r="F44" s="5">
         <f t="shared" si="2"/>
-        <v>33369.591065807224</v>
+        <v>7818.8947646468378</v>
       </c>
       <c r="G44" s="6">
-        <v>9.6499996185302717</v>
+        <v>23.379999160766602</v>
       </c>
       <c r="H44" s="7">
         <f t="shared" si="3"/>
-        <v>322016.54105555086</v>
+        <v>182805.75303556543</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="C45" s="9" t="s">
         <v>10</v>
       </c>
       <c r="D45" s="10">
-        <v>37858</v>
+        <v>37418</v>
       </c>
       <c r="E45" s="10">
-        <v>296007718</v>
+        <v>373751274</v>
       </c>
       <c r="F45" s="11">
         <f t="shared" si="2"/>
-        <v>7818.8947646468378</v>
+        <v>9988.5422523918969</v>
       </c>
       <c r="G45" s="12">
-        <v>23.379999160766602</v>
+        <v>4</v>
       </c>
       <c r="H45" s="13">
         <f t="shared" si="3"/>
-        <v>182805.75303556543</v>
+        <v>39954.169009567588</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D46" s="4">
-        <v>37418</v>
+        <v>33810</v>
       </c>
       <c r="E46" s="4">
-        <v>373751274</v>
+        <v>275619506</v>
       </c>
       <c r="F46" s="5">
         <f t="shared" si="2"/>
-        <v>9988.5422523918969</v>
+        <v>8152.0114167406091</v>
       </c>
       <c r="G46" s="6">
-        <v>4</v>
+        <v>6.630000114440918</v>
       </c>
       <c r="H46" s="7">
         <f t="shared" si="3"/>
-        <v>39954.169009567588</v>
+        <v>54047.836625913907</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D47" s="10">
-        <v>33810</v>
+        <v>32818</v>
       </c>
       <c r="E47" s="10">
-        <v>275619506</v>
+        <v>1406822230</v>
       </c>
       <c r="F47" s="11">
         <f t="shared" si="2"/>
-        <v>8152.0114167406091</v>
+        <v>42867.396855384242</v>
       </c>
       <c r="G47" s="12">
-        <v>6.630000114440918</v>
+        <v>14.69999980926514</v>
       </c>
       <c r="H47" s="13">
         <f t="shared" si="3"/>
-        <v>54047.836625913907</v>
+        <v>630150.72559784143</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="D48" s="4">
-        <v>32818</v>
+        <v>30608</v>
       </c>
       <c r="E48" s="4">
-        <v>1406822230</v>
+        <v>1067930953</v>
       </c>
       <c r="F48" s="5">
         <f t="shared" si="2"/>
-        <v>42867.396855384242</v>
+        <v>34890.582625457399</v>
       </c>
       <c r="G48" s="6">
-        <v>14.69999980926514</v>
+        <v>38.430000305175781</v>
       </c>
       <c r="H48" s="7">
         <f t="shared" si="3"/>
-        <v>630150.72559784143</v>
+        <v>1340845.1009440885</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>10</v>
+        <v>129</v>
       </c>
       <c r="D49" s="10">
-        <v>30608</v>
+        <v>30099</v>
       </c>
       <c r="E49" s="10">
-        <v>1067930953</v>
+        <v>123583436</v>
       </c>
       <c r="F49" s="11">
         <f t="shared" si="2"/>
-        <v>34890.582625457399</v>
+        <v>4105.8984019402642</v>
       </c>
       <c r="G49" s="12">
-        <v>38.430000305175781</v>
+        <v>20</v>
       </c>
       <c r="H49" s="13">
         <f t="shared" si="3"/>
-        <v>1340845.1009440885</v>
+        <v>82117.96803880528</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>111</v>
+        <v>56</v>
       </c>
       <c r="D50" s="4">
-        <v>30099</v>
+        <v>28962</v>
       </c>
       <c r="E50" s="4">
-        <v>123583436</v>
+        <v>1002045228</v>
       </c>
       <c r="F50" s="5">
         <f t="shared" si="2"/>
-        <v>4105.8984019402642</v>
+        <v>34598.61984669567</v>
       </c>
       <c r="G50" s="6">
-        <v>20</v>
+        <v>16.360000610351559</v>
       </c>
       <c r="H50" s="7">
         <f t="shared" si="3"/>
-        <v>82117.96803880528</v>
+        <v>566033.44180926273</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>10</v>
+        <v>134</v>
       </c>
       <c r="D51" s="10">
-        <v>28962</v>
+        <v>27934</v>
       </c>
       <c r="E51" s="10">
-        <v>1002045228</v>
+        <v>1603651339</v>
       </c>
       <c r="F51" s="11">
         <f t="shared" si="2"/>
-        <v>34598.61984669567</v>
+        <v>57408.582336937063</v>
       </c>
       <c r="G51" s="12">
-        <v>16.360000610351559</v>
+        <v>3.7000000476837158</v>
       </c>
       <c r="H51" s="13">
         <f t="shared" si="3"/>
-        <v>566033.44180926273</v>
+        <v>212411.75738412165</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>10</v>
+        <v>137</v>
       </c>
       <c r="D52" s="4">
-        <v>27934</v>
+        <v>26713</v>
       </c>
       <c r="E52" s="4">
-        <v>1603651339</v>
+        <v>322143505</v>
       </c>
       <c r="F52" s="5">
         <f t="shared" si="2"/>
-        <v>57408.582336937063</v>
+        <v>12059.428181035451</v>
       </c>
       <c r="G52" s="6">
-        <v>3.7000000476837158</v>
+        <v>30.190000534057621</v>
       </c>
       <c r="H52" s="7">
         <f t="shared" si="3"/>
-        <v>212411.75738412165</v>
+        <v>364074.14322588983</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D53" s="10">
-        <v>26713</v>
+        <v>19071</v>
       </c>
       <c r="E53" s="10">
-        <v>322143505</v>
+        <v>247852006</v>
       </c>
       <c r="F53" s="11">
         <f t="shared" si="2"/>
-        <v>12059.428181035451</v>
+        <v>12996.277384510513</v>
       </c>
       <c r="G53" s="12">
-        <v>30.190000534057621</v>
+        <v>10.14999961853027</v>
       </c>
       <c r="H53" s="13">
         <f t="shared" si="3"/>
-        <v>364074.14322588983</v>
+        <v>131912.21049509529</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="D54" s="4">
-        <v>19071</v>
+        <v>30</v>
       </c>
       <c r="E54" s="4">
-        <v>247852006</v>
+        <v>722</v>
       </c>
       <c r="F54" s="5">
         <f t="shared" si="2"/>
-        <v>12996.277384510513</v>
+        <v>24.066666666666666</v>
       </c>
       <c r="G54" s="6">
-        <v>10.14999961853027</v>
+        <v>51.529998779296882</v>
       </c>
       <c r="H54" s="7">
         <f t="shared" si="3"/>
-        <v>131912.21049509529</v>
+        <v>1240.1553039550784</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>10</v>
+        <v>144</v>
       </c>
       <c r="D55" s="10">
         <v>1</v>
@@ -2857,13 +2938,13 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="D56" s="4">
         <v>1</v>
@@ -2885,13 +2966,13 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>10</v>
+        <v>149</v>
       </c>
       <c r="D57" s="10">
         <v>1</v>
@@ -2913,40 +2994,40 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>126</v>
+        <v>150</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>127</v>
+        <v>151</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>10</v>
+        <v>152</v>
       </c>
       <c r="D58" s="4">
         <v>275691</v>
       </c>
       <c r="E58" s="4">
-        <v>2854464053</v>
+        <v>2812830199</v>
       </c>
       <c r="F58" s="5">
         <f t="shared" si="2"/>
-        <v>10353.852875139195</v>
+        <v>10202.836505362888</v>
       </c>
       <c r="G58" s="20" t="s">
-        <v>128</v>
+        <v>153</v>
       </c>
       <c r="H58" s="21" t="s">
-        <v>129</v>
+        <v>154</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>130</v>
+        <v>155</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>131</v>
+        <v>156</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="D59" s="10">
         <v>104168</v>
@@ -2959,21 +3040,21 @@
         <v>7060.4306696874282</v>
       </c>
       <c r="G59" s="22" t="s">
-        <v>128</v>
+        <v>153</v>
       </c>
       <c r="H59" s="23" t="s">
-        <v>129</v>
+        <v>154</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>132</v>
+        <v>157</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>133</v>
+        <v>158</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>10</v>
+        <v>159</v>
       </c>
       <c r="D60" s="4">
         <v>92398</v>
@@ -2986,21 +3067,21 @@
         <v>7703.98862529492</v>
       </c>
       <c r="G60" s="20" t="s">
-        <v>128</v>
+        <v>153</v>
       </c>
       <c r="H60" s="21" t="s">
-        <v>129</v>
+        <v>154</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>134</v>
+        <v>160</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>135</v>
+        <v>161</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="D61" s="10">
         <v>89966</v>
@@ -3013,18 +3094,18 @@
         <v>20607.033912811508</v>
       </c>
       <c r="G61" s="22" t="s">
-        <v>128</v>
+        <v>153</v>
       </c>
       <c r="H61" s="23" t="s">
-        <v>129</v>
+        <v>154</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>138</v>
+        <v>164</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>10</v>
@@ -3040,21 +3121,21 @@
         <v>45969.403579026402</v>
       </c>
       <c r="G62" s="20" t="s">
-        <v>128</v>
+        <v>153</v>
       </c>
       <c r="H62" s="21" t="s">
-        <v>129</v>
+        <v>154</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>140</v>
+        <v>166</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>10</v>
+        <v>167</v>
       </c>
       <c r="D63" s="10">
         <v>1</v>
@@ -3067,15 +3148,15 @@
         <v>0</v>
       </c>
       <c r="G63" s="22" t="s">
-        <v>128</v>
+        <v>153</v>
       </c>
       <c r="H63" s="23" t="s">
-        <v>129</v>
+        <v>154</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="24" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B65" s="25"/>
       <c r="C65" s="25"/>
@@ -3087,7 +3168,7 @@
     </row>
     <row r="66" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="24" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B66" s="25"/>
       <c r="C66" s="25"/>
@@ -3099,7 +3180,7 @@
     </row>
     <row r="67" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="24" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B67" s="25"/>
       <c r="C67" s="25"/>
@@ -3111,7 +3192,7 @@
     </row>
     <row r="68" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="24" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B68" s="25"/>
       <c r="C68" s="25"/>
